--- a/database/event/3891/event_3891_evp_summary.xlsx
+++ b/database/event/3891/event_3891_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.9282</v>
+        <v>8.208</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8086</v>
+        <v>2.1427</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3775</v>
+        <v>2.8262</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9282</v>
+        <v>8.208</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4473</v>
+        <v>3.7271</v>
       </c>
       <c r="G2" t="n">
         <v>4.4809</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4473</v>
+        <v>3.7271</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4473</v>
+        <v>3.7271</v>
       </c>
       <c r="J2" t="n">
         <v>4.4809</v>
@@ -529,7 +529,7 @@
         <v>275</v>
       </c>
       <c r="M2" t="n">
-        <v>6.9282</v>
+        <v>8.208</v>
       </c>
       <c r="N2" t="n">
         <v>353</v>
@@ -548,7 +548,7 @@
         <v>1.7666</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3124</v>
+        <v>2.2521</v>
       </c>
       <c r="E3" t="n">
         <v>6.7672</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.5353</v>
+        <v>6.7082</v>
       </c>
       <c r="C4" t="n">
-        <v>1.706</v>
+        <v>1.7512</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2188</v>
+        <v>2.2286</v>
       </c>
       <c r="E4" t="n">
-        <v>6.5353</v>
+        <v>6.7082</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2927</v>
+        <v>1.4656</v>
       </c>
       <c r="G4" t="n">
         <v>5.2426</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2927</v>
+        <v>1.4656</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2927</v>
+        <v>1.4656</v>
       </c>
       <c r="J4" t="n">
         <v>5.2426</v>
@@ -621,7 +621,7 @@
         <v>275</v>
       </c>
       <c r="M4" t="n">
-        <v>6.5353</v>
+        <v>6.708200000000001</v>
       </c>
       <c r="N4" t="n">
         <v>353</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.8671</v>
+        <v>6.5153</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5316</v>
+        <v>1.7008</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9488</v>
+        <v>2.1518</v>
       </c>
       <c r="E5" t="n">
-        <v>5.8671</v>
+        <v>6.5153</v>
       </c>
       <c r="F5" t="n">
-        <v>2.281</v>
+        <v>2.9292</v>
       </c>
       <c r="G5" t="n">
         <v>3.5861</v>
       </c>
       <c r="H5" t="n">
-        <v>2.281</v>
+        <v>2.9292</v>
       </c>
       <c r="I5" t="n">
-        <v>2.281</v>
+        <v>2.9292</v>
       </c>
       <c r="J5" t="n">
         <v>3.5861</v>
@@ -667,7 +667,7 @@
         <v>140</v>
       </c>
       <c r="M5" t="n">
-        <v>5.867100000000001</v>
+        <v>6.5153</v>
       </c>
       <c r="N5" t="n">
         <v>225</v>
@@ -676,139 +676,139 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9103</v>
+        <v>5.2294</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0208</v>
+        <v>1.3651</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1583</v>
+        <v>1.6395</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9103</v>
+        <v>5.2294</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0217</v>
+        <v>4.2762</v>
       </c>
       <c r="G6" t="n">
-        <v>3.8886</v>
+        <v>0.9532</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0217</v>
+        <v>4.4021</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0217</v>
+        <v>4.4021</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8886</v>
+        <v>0.9532</v>
       </c>
       <c r="K6" t="n">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="L6" t="n">
-        <v>269</v>
+        <v>99</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9103</v>
+        <v>5.3553</v>
       </c>
       <c r="N6" t="n">
-        <v>406</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>jR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.864</v>
+        <v>4.5026</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0087</v>
+        <v>1.1754</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1396</v>
+        <v>1.3499</v>
       </c>
       <c r="E7" t="n">
-        <v>3.864</v>
+        <v>4.5026</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9108</v>
+        <v>3.6832</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9532</v>
+        <v>0.8194</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9108</v>
+        <v>3.6832</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9108</v>
+        <v>3.6832</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9532</v>
+        <v>0.8194</v>
       </c>
       <c r="K7" t="n">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="L7" t="n">
-        <v>99</v>
+        <v>269</v>
       </c>
       <c r="M7" t="n">
-        <v>3.864</v>
+        <v>4.5026</v>
       </c>
       <c r="N7" t="n">
-        <v>195</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>jR</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7863</v>
+        <v>4.3611</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9883999999999999</v>
+        <v>1.1385</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1082</v>
+        <v>1.2936</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7863</v>
+        <v>4.3611</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9669</v>
+        <v>2.9463</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8194</v>
+        <v>1.4148</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9669</v>
+        <v>2.9463</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9669</v>
+        <v>2.9463</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8194</v>
+        <v>1.4148</v>
       </c>
       <c r="K8" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L8" t="n">
-        <v>269</v>
+        <v>93</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7863</v>
+        <v>4.3611</v>
       </c>
       <c r="N8" t="n">
-        <v>406</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.256</v>
+        <v>4.2509</v>
       </c>
       <c r="C9" t="n">
-        <v>0.85</v>
+        <v>1.1097</v>
       </c>
       <c r="D9" t="n">
-        <v>0.894</v>
+        <v>1.2496</v>
       </c>
       <c r="E9" t="n">
-        <v>3.256</v>
+        <v>4.2509</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0786</v>
+        <v>3.0735</v>
       </c>
       <c r="G9" t="n">
         <v>1.1774</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0786</v>
+        <v>3.0735</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0786</v>
+        <v>3.0735</v>
       </c>
       <c r="J9" t="n">
         <v>1.1774</v>
@@ -851,7 +851,7 @@
         <v>140</v>
       </c>
       <c r="M9" t="n">
-        <v>3.256</v>
+        <v>4.2509</v>
       </c>
       <c r="N9" t="n">
         <v>225</v>
@@ -860,47 +860,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2284</v>
+        <v>4.2245</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8428</v>
+        <v>1.1028</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8828</v>
+        <v>1.2391</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2284</v>
+        <v>4.2245</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8136</v>
+        <v>0.3359</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4148</v>
+        <v>3.8886</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8136</v>
+        <v>0.3359</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8136</v>
+        <v>0.3359</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4148</v>
+        <v>3.8886</v>
       </c>
       <c r="K10" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L10" t="n">
-        <v>93</v>
+        <v>269</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2284</v>
+        <v>4.2245</v>
       </c>
       <c r="N10" t="n">
-        <v>232</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4601</v>
+        <v>3.151</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6422</v>
+        <v>0.8226</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5725</v>
+        <v>0.8114</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4601</v>
+        <v>3.151</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4601</v>
+        <v>3.151</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4601</v>
+        <v>3.151</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4601</v>
+        <v>3.151</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4601</v>
+        <v>3.151</v>
       </c>
       <c r="N11" t="n">
         <v>141</v>
@@ -952,584 +952,584 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tonyblack</t>
+          <t>xseveN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3257</v>
+        <v>2.9369</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6071</v>
+        <v>0.7667</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5182</v>
+        <v>0.7262</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3257</v>
+        <v>2.9369</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1308</v>
+        <v>2.0396</v>
       </c>
       <c r="G12" t="n">
-        <v>3.4565</v>
+        <v>0.8973</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1308</v>
+        <v>2.0396</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1308</v>
+        <v>2.0396</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4565</v>
+        <v>0.8973</v>
       </c>
       <c r="K12" t="n">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="L12" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3257</v>
+        <v>2.9369</v>
       </c>
       <c r="N12" t="n">
-        <v>406</v>
+        <v>353</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>xseveN</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.287</v>
+        <v>2.8269</v>
       </c>
       <c r="C13" t="n">
-        <v>0.597</v>
+        <v>0.738</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.6823</v>
       </c>
       <c r="E13" t="n">
-        <v>2.287</v>
+        <v>2.8269</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3897</v>
+        <v>2.8269</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8973</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3897</v>
+        <v>2.8269</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3897</v>
+        <v>2.8269</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8973</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="L13" t="n">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.287</v>
+        <v>2.8269</v>
       </c>
       <c r="N13" t="n">
-        <v>353</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>refrezh</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0232</v>
+        <v>2.7416</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5282</v>
+        <v>0.7157</v>
       </c>
       <c r="D14" t="n">
-        <v>0.396</v>
+        <v>0.6483</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0232</v>
+        <v>2.7416</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3556</v>
+        <v>3.0227</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3788</v>
+        <v>-0.2811</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3556</v>
+        <v>3.0227</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3556</v>
+        <v>3.0227</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3788</v>
+        <v>-0.2811</v>
       </c>
       <c r="K14" t="n">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="L14" t="n">
-        <v>275</v>
+        <v>55</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0232</v>
+        <v>2.7416</v>
       </c>
       <c r="N14" t="n">
-        <v>353</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>smooya</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9519</v>
+        <v>2.7204</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5095</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3672</v>
+        <v>0.6399</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9519</v>
+        <v>2.7204</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7513</v>
+        <v>2.4799</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2006</v>
+        <v>0.2405</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7513</v>
+        <v>2.4799</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7513</v>
+        <v>2.4799</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2006</v>
+        <v>0.2405</v>
       </c>
       <c r="K15" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="L15" t="n">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9519</v>
+        <v>2.7204</v>
       </c>
       <c r="N15" t="n">
-        <v>194</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8534</v>
+        <v>2.6853</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4838</v>
+        <v>0.701</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3274</v>
+        <v>0.6259</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8534</v>
+        <v>2.6853</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2435</v>
+        <v>2.4847</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6099</v>
+        <v>0.2006</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2435</v>
+        <v>2.4847</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2435</v>
+        <v>2.4847</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6099</v>
+        <v>0.2006</v>
       </c>
       <c r="K16" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="L16" t="n">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8534</v>
+        <v>2.6853</v>
       </c>
       <c r="N16" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>tonyblack</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8175</v>
+        <v>2.5109</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4745</v>
+        <v>0.6555</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3129</v>
+        <v>0.5564</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8175</v>
+        <v>2.5109</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8175</v>
+        <v>-0.9456</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3.4565</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8175</v>
+        <v>-0.9456</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8175</v>
+        <v>-0.9456</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3.4565</v>
       </c>
       <c r="K17" t="n">
         <v>137</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8175</v>
+        <v>2.5109</v>
       </c>
       <c r="N17" t="n">
-        <v>137</v>
+        <v>406</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>nukkye</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7271</v>
+        <v>2.4267</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4509</v>
+        <v>0.6335</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2763</v>
+        <v>0.5229</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7271</v>
+        <v>2.4267</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7271</v>
+        <v>2.4267</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7271</v>
+        <v>2.4267</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7271</v>
+        <v>2.4267</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7271</v>
+        <v>2.4267</v>
       </c>
       <c r="N18" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>smooya</t>
+          <t>bottle</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6593</v>
+        <v>2.3528</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4332</v>
+        <v>0.6142</v>
       </c>
       <c r="D19" t="n">
-        <v>0.249</v>
+        <v>0.4934</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6593</v>
+        <v>2.3528</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4188</v>
+        <v>2.3528</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2405</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4188</v>
+        <v>2.3528</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4188</v>
+        <v>2.3528</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2405</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="L19" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6593</v>
+        <v>2.3528</v>
       </c>
       <c r="N19" t="n">
-        <v>232</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>EspiranTo</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6168</v>
+        <v>2.338</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4221</v>
+        <v>0.6103</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2318</v>
+        <v>0.4875</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6168</v>
+        <v>2.338</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6168</v>
+        <v>2.338</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6168</v>
+        <v>2.338</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6168</v>
+        <v>2.338</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.6168</v>
+        <v>2.338</v>
       </c>
       <c r="N20" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.5046</v>
+        <v>2.0932</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3928</v>
+        <v>0.5464</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1865</v>
+        <v>0.39</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5046</v>
+        <v>2.0932</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3848</v>
+        <v>2.4419</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1198</v>
+        <v>-0.3487</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3848</v>
+        <v>2.4419</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3848</v>
+        <v>2.4419</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1198</v>
+        <v>-0.3487</v>
       </c>
       <c r="K21" t="n">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="L21" t="n">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="M21" t="n">
-        <v>1.5046</v>
+        <v>2.0932</v>
       </c>
       <c r="N21" t="n">
-        <v>161</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bottle</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4723</v>
+        <v>2.0232</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3843</v>
+        <v>0.5282</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1734</v>
+        <v>0.3621</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4723</v>
+        <v>2.0232</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4723</v>
+        <v>-0.3556</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2.3788</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4723</v>
+        <v>-0.3556</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4723</v>
+        <v>-0.3556</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2.3788</v>
       </c>
       <c r="K22" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4723</v>
+        <v>2.0232</v>
       </c>
       <c r="N22" t="n">
-        <v>87</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.413</v>
+        <v>1.9201</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3689</v>
+        <v>0.5012</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1495</v>
+        <v>0.3211</v>
       </c>
       <c r="E23" t="n">
-        <v>1.413</v>
+        <v>1.9201</v>
       </c>
       <c r="F23" t="n">
-        <v>1.413</v>
+        <v>1.9201</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.413</v>
+        <v>1.9201</v>
       </c>
       <c r="I23" t="n">
-        <v>1.413</v>
+        <v>1.9201</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.413</v>
+        <v>1.9201</v>
       </c>
       <c r="N23" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EspiranTo</t>
+          <t>nukkye</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.4073</v>
+        <v>1.912</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3674</v>
+        <v>0.4991</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1472</v>
+        <v>0.3178</v>
       </c>
       <c r="E24" t="n">
-        <v>1.4073</v>
+        <v>1.912</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4073</v>
+        <v>1.912</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4073</v>
+        <v>1.912</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4073</v>
+        <v>1.912</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.4073</v>
+        <v>1.912</v>
       </c>
       <c r="N24" t="n">
         <v>132</v>
@@ -1550,599 +1550,599 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>refrezh</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3377</v>
+        <v>1.8567</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3492</v>
+        <v>0.4847</v>
       </c>
       <c r="D25" t="n">
-        <v>0.119</v>
+        <v>0.2958</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3377</v>
+        <v>1.8567</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6188</v>
+        <v>1.2468</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2811</v>
+        <v>0.6099</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6188</v>
+        <v>1.2468</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6188</v>
+        <v>1.2468</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2811</v>
+        <v>0.6099</v>
       </c>
       <c r="K25" t="n">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="L25" t="n">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="M25" t="n">
-        <v>1.3377</v>
+        <v>1.8567</v>
       </c>
       <c r="N25" t="n">
-        <v>166</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.2714</v>
+        <v>1.8099</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3319</v>
+        <v>0.4725</v>
       </c>
       <c r="D26" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.2772</v>
       </c>
       <c r="E26" t="n">
-        <v>1.2714</v>
+        <v>1.8099</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0749</v>
+        <v>1.6901</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1965</v>
+        <v>0.1198</v>
       </c>
       <c r="H26" t="n">
-        <v>1.0749</v>
+        <v>1.6901</v>
       </c>
       <c r="I26" t="n">
-        <v>1.0749</v>
+        <v>1.6901</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1965</v>
+        <v>0.1198</v>
       </c>
       <c r="K26" t="n">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="L26" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M26" t="n">
-        <v>1.2714</v>
+        <v>1.8099</v>
       </c>
       <c r="N26" t="n">
-        <v>194</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.1501</v>
+        <v>1.678</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3002</v>
+        <v>0.438</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0433</v>
+        <v>0.2246</v>
       </c>
       <c r="E27" t="n">
-        <v>1.1501</v>
+        <v>1.678</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1501</v>
+        <v>1.678</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1501</v>
+        <v>1.678</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1501</v>
+        <v>1.678</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1501</v>
+        <v>1.678</v>
       </c>
       <c r="N27" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1448</v>
+        <v>1.6691</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2988</v>
+        <v>0.4357</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0411</v>
+        <v>0.2211</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1448</v>
+        <v>1.6691</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3686</v>
+        <v>1.4726</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7762</v>
+        <v>0.1965</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3686</v>
+        <v>1.4726</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3686</v>
+        <v>1.4726</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7762</v>
+        <v>0.1965</v>
       </c>
       <c r="K28" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="L28" t="n">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1448</v>
+        <v>1.6691</v>
       </c>
       <c r="N28" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.0949</v>
+        <v>1.6261</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2858</v>
+        <v>0.4245</v>
       </c>
       <c r="D29" t="n">
-        <v>0.021</v>
+        <v>0.2039</v>
       </c>
       <c r="E29" t="n">
-        <v>1.0949</v>
+        <v>1.6261</v>
       </c>
       <c r="F29" t="n">
-        <v>1.0949</v>
+        <v>1.6261</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.0949</v>
+        <v>1.6261</v>
       </c>
       <c r="I29" t="n">
-        <v>1.0949</v>
+        <v>1.6261</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.0949</v>
+        <v>1.6261</v>
       </c>
       <c r="N29" t="n">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.0384</v>
+        <v>1.3376</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2711</v>
+        <v>0.3492</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0019</v>
+        <v>0.089</v>
       </c>
       <c r="E30" t="n">
-        <v>1.0384</v>
+        <v>1.3376</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1376</v>
+        <v>1.4078</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0992</v>
+        <v>-0.0702</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1376</v>
+        <v>1.4078</v>
       </c>
       <c r="I30" t="n">
-        <v>1.1376</v>
+        <v>1.4078</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.0992</v>
+        <v>-0.0702</v>
       </c>
       <c r="K30" t="n">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="L30" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M30" t="n">
-        <v>1.0384</v>
+        <v>1.3376</v>
       </c>
       <c r="N30" t="n">
-        <v>161</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.0319</v>
+        <v>1.1931</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2694</v>
+        <v>0.3115</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0045</v>
+        <v>0.0314</v>
       </c>
       <c r="E31" t="n">
-        <v>1.0319</v>
+        <v>1.1931</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3806</v>
+        <v>1.1931</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.3487</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.3806</v>
+        <v>1.1931</v>
       </c>
       <c r="I31" t="n">
-        <v>1.3806</v>
+        <v>1.1931</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.3487</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="L31" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.0319</v>
+        <v>1.1931</v>
       </c>
       <c r="N31" t="n">
-        <v>195</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9335</v>
+        <v>1.1448</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2437</v>
+        <v>0.2988</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0442</v>
+        <v>0.0122</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9335</v>
+        <v>1.1448</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9335</v>
+        <v>0.3686</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.7762</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9335</v>
+        <v>0.3686</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9335</v>
+        <v>0.3686</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.7762</v>
       </c>
       <c r="K32" t="n">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9335</v>
+        <v>1.1448</v>
       </c>
       <c r="N32" t="n">
-        <v>141</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8502</v>
+        <v>1.1212</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2219</v>
+        <v>0.2927</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0779</v>
+        <v>0.0028</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8502</v>
+        <v>1.1212</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9204</v>
+        <v>1.2204</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.0702</v>
+        <v>-0.0992</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9204</v>
+        <v>1.2204</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9204</v>
+        <v>1.2204</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.0702</v>
+        <v>-0.0992</v>
       </c>
       <c r="K33" t="n">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="L33" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8502</v>
+        <v>1.1212</v>
       </c>
       <c r="N33" t="n">
-        <v>194</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8064</v>
+        <v>1.1118</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2105</v>
+        <v>0.2902</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0956</v>
+        <v>-0.001</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8064</v>
+        <v>1.1118</v>
       </c>
       <c r="F34" t="n">
-        <v>1.7169</v>
+        <v>1.1118</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.9105</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.7169</v>
+        <v>1.1118</v>
       </c>
       <c r="I34" t="n">
-        <v>1.7169</v>
+        <v>1.1118</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9105</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L34" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8064000000000001</v>
+        <v>1.1118</v>
       </c>
       <c r="N34" t="n">
-        <v>161</v>
+        <v>137</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6749000000000001</v>
+        <v>1.1094</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1762</v>
+        <v>0.2896</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1487</v>
+        <v>-0.0019</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6749000000000001</v>
+        <v>1.1094</v>
       </c>
       <c r="F35" t="n">
-        <v>1.7133</v>
+        <v>2.0199</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.0384</v>
+        <v>-0.9105</v>
       </c>
       <c r="H35" t="n">
-        <v>1.7133</v>
+        <v>2.0199</v>
       </c>
       <c r="I35" t="n">
-        <v>1.7133</v>
+        <v>2.0199</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.0384</v>
+        <v>-0.9105</v>
       </c>
       <c r="K35" t="n">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="L35" t="n">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6749000000000001</v>
+        <v>1.1094</v>
       </c>
       <c r="N35" t="n">
-        <v>225</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6714</v>
+        <v>0.9421</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1753</v>
+        <v>0.2459</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1501</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6714</v>
+        <v>0.9421</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6714</v>
+        <v>1.9805</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-1.0384</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6714</v>
+        <v>1.9805</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6714</v>
+        <v>1.9805</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-1.0384</v>
       </c>
       <c r="K36" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6714</v>
+        <v>0.9420999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>99</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5907</v>
+        <v>0.6714</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1542</v>
+        <v>0.1753</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1827</v>
+        <v>-0.1764</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5907</v>
+        <v>0.6714</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5907</v>
+        <v>0.6714</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5907</v>
+        <v>0.6714</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5907</v>
+        <v>0.6714</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.5907</v>
+        <v>0.6714</v>
       </c>
       <c r="N37" t="n">
-        <v>137</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38">
@@ -2158,7 +2158,7 @@
         <v>0.153</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1846</v>
+        <v>-0.2104</v>
       </c>
       <c r="E38" t="n">
         <v>0.586</v>
@@ -2194,231 +2194,231 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.421</v>
+        <v>0.5299</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1099</v>
+        <v>0.1383</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2513</v>
+        <v>-0.2328</v>
       </c>
       <c r="E39" t="n">
-        <v>0.421</v>
+        <v>0.5299</v>
       </c>
       <c r="F39" t="n">
-        <v>0.421</v>
+        <v>0.5299</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.421</v>
+        <v>0.5299</v>
       </c>
       <c r="I39" t="n">
-        <v>0.421</v>
+        <v>0.5299</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.421</v>
+        <v>0.5299</v>
       </c>
       <c r="N39" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>hutji</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4172</v>
+        <v>0.5049</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1089</v>
+        <v>0.1318</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2528</v>
+        <v>-0.2428</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4172</v>
+        <v>0.5049</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4172</v>
+        <v>1.3151</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.8102</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4172</v>
+        <v>1.3151</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4172</v>
+        <v>1.3151</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.8102</v>
       </c>
       <c r="K40" t="n">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4172</v>
+        <v>0.5048999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>79</v>
+        <v>406</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>xccurate</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3238</v>
+        <v>0.421</v>
       </c>
       <c r="C41" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.1099</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2906</v>
+        <v>-0.2762</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3238</v>
+        <v>0.421</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3238</v>
+        <v>0.421</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3238</v>
+        <v>0.421</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3238</v>
+        <v>0.421</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3238</v>
+        <v>0.421</v>
       </c>
       <c r="N41" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.2674</v>
+        <v>0.4172</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0698</v>
+        <v>0.1089</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3133</v>
+        <v>-0.2777</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2674</v>
+        <v>0.4172</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2674</v>
+        <v>0.4172</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2674</v>
+        <v>0.4172</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2674</v>
+        <v>0.4172</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2674</v>
+        <v>0.4172</v>
       </c>
       <c r="N42" t="n">
-        <v>104</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>hutji</t>
+          <t>xccurate</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2294</v>
+        <v>0.3238</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0599</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3287</v>
+        <v>-0.3149</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2294</v>
+        <v>0.3238</v>
       </c>
       <c r="F43" t="n">
-        <v>1.0396</v>
+        <v>0.3238</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.8102</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.0396</v>
+        <v>0.3238</v>
       </c>
       <c r="I43" t="n">
-        <v>1.0396</v>
+        <v>0.3238</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.8102</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L43" t="n">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2294</v>
+        <v>0.3238</v>
       </c>
       <c r="N43" t="n">
-        <v>406</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44">
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.1673</v>
+        <v>0.2005</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0437</v>
+        <v>0.0523</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3538</v>
+        <v>-0.364</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1673</v>
+        <v>0.2005</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8374</v>
+        <v>0.8706</v>
       </c>
       <c r="G44" t="n">
         <v>-0.6701</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8374</v>
+        <v>0.8706</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8374</v>
+        <v>0.8706</v>
       </c>
       <c r="J44" t="n">
         <v>-0.6701</v>
@@ -2461,7 +2461,7 @@
         <v>50</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1673</v>
+        <v>0.2005</v>
       </c>
       <c r="N44" t="n">
         <v>161</v>
@@ -2480,7 +2480,7 @@
         <v>0.0345</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3679</v>
+        <v>-0.3912</v>
       </c>
       <c r="E45" t="n">
         <v>0.1323</v>
@@ -2526,7 +2526,7 @@
         <v>0.023</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3858</v>
+        <v>-0.4089</v>
       </c>
       <c r="E46" t="n">
         <v>0.08799999999999999</v>
@@ -2562,93 +2562,93 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>faveN</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.0128</v>
+        <v>0.0146</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0033</v>
+        <v>0.0038</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4265</v>
+        <v>-0.4381</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0128</v>
+        <v>0.0146</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.0128</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.6935</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.0128</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0128</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>0.6935</v>
       </c>
       <c r="K47" t="n">
+        <v>96</v>
+      </c>
+      <c r="L47" t="n">
         <v>99</v>
       </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
       <c r="M47" t="n">
-        <v>-0.0128</v>
+        <v>0.01460000000000006</v>
       </c>
       <c r="N47" t="n">
-        <v>99</v>
+        <v>195</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>faveN</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0543</v>
+        <v>-0.0128</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0142</v>
+        <v>-0.0033</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4433</v>
+        <v>-0.449</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0543</v>
+        <v>-0.0128</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.7478</v>
+        <v>-0.0128</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6935</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.7478</v>
+        <v>-0.0128</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.7478</v>
+        <v>-0.0128</v>
       </c>
       <c r="J48" t="n">
-        <v>0.6935</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="N48" t="n">
         <v>99</v>
-      </c>
-      <c r="M48" t="n">
-        <v>-0.05430000000000001</v>
-      </c>
-      <c r="N48" t="n">
-        <v>195</v>
       </c>
     </row>
     <row r="49">
@@ -2664,7 +2664,7 @@
         <v>-0.037</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4786</v>
+        <v>-0.5003</v>
       </c>
       <c r="E49" t="n">
         <v>-0.1416</v>
@@ -2700,308 +2700,308 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.3255</v>
+        <v>-0.2475</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.0646</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5528999999999999</v>
+        <v>-0.5425</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.3255</v>
+        <v>-0.2475</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2683</v>
+        <v>-0.2475</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.5938</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2683</v>
+        <v>-0.2475</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2683</v>
+        <v>-0.2475</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.5938</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L50" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.3255</v>
+        <v>-0.2475</v>
       </c>
       <c r="N50" t="n">
-        <v>194</v>
+        <v>137</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.3435</v>
+        <v>-0.2882</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0897</v>
+        <v>-0.0752</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5601</v>
+        <v>-0.5587</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.3435</v>
+        <v>-0.2882</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.3435</v>
+        <v>0.3056</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-0.5938</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.3435</v>
+        <v>0.3056</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3435</v>
+        <v>0.3056</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-0.5938</v>
       </c>
       <c r="K51" t="n">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.3435</v>
+        <v>-0.2882</v>
       </c>
       <c r="N51" t="n">
-        <v>111</v>
+        <v>194</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.393</v>
+        <v>-0.3435</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1026</v>
+        <v>-0.0897</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5808</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.393</v>
+        <v>-0.3435</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.393</v>
+        <v>-0.3435</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.393</v>
+        <v>-0.3435</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.393</v>
+        <v>-0.3435</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.393</v>
+        <v>-0.3435</v>
       </c>
       <c r="N52" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.514</v>
+        <v>-0.3467</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1342</v>
+        <v>-0.0905</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.629</v>
+        <v>-0.582</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.514</v>
+        <v>-0.3467</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.514</v>
+        <v>-0.3467</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.514</v>
+        <v>-0.3467</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.514</v>
+        <v>-0.3467</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.514</v>
+        <v>-0.3467</v>
       </c>
       <c r="N53" t="n">
-        <v>141</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.5585</v>
+        <v>-0.514</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1458</v>
+        <v>-0.1342</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.647</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.5585</v>
+        <v>-0.514</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.5585</v>
+        <v>-0.514</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.5585</v>
+        <v>-0.514</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.5585</v>
+        <v>-0.514</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.5585</v>
+        <v>-0.514</v>
       </c>
       <c r="N54" t="n">
-        <v>111</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.5735</v>
+        <v>-0.5585</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1497</v>
+        <v>-0.1458</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.653</v>
+        <v>-0.6664</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.5735</v>
+        <v>-0.5585</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.5735</v>
+        <v>-0.5585</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.5735</v>
+        <v>-0.5585</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5735</v>
+        <v>-0.5585</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.5735</v>
+        <v>-0.5585</v>
       </c>
       <c r="N55" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NaToSaphiX</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.5893</v>
+        <v>-0.5735</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1538</v>
+        <v>-0.1497</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6594</v>
+        <v>-0.6724</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.5893</v>
+        <v>-0.5735</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.5893</v>
+        <v>-0.5735</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.5893</v>
+        <v>-0.5735</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5893</v>
+        <v>-0.5735</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.5893</v>
+        <v>-0.5735</v>
       </c>
       <c r="N56" t="n">
         <v>99</v>
@@ -3022,323 +3022,323 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>NaToSaphiX</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.6273</v>
+        <v>-0.5893</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1638</v>
+        <v>-0.1538</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6748</v>
+        <v>-0.6787</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.6273</v>
+        <v>-0.5893</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.6273</v>
+        <v>-0.5893</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.6273</v>
+        <v>-0.5893</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.6273</v>
+        <v>-0.5893</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.6273</v>
+        <v>-0.5893</v>
       </c>
       <c r="N57" t="n">
-        <v>137</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>dephh</t>
+          <t>pounh</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1886</v>
+        <v>-0.1772</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.7131999999999999</v>
+        <v>-0.7144</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>79</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PERCY</t>
+          <t>dephh</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.728</v>
+        <v>-0.7223000000000001</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.19</v>
+        <v>-0.1886</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7155</v>
+        <v>-0.7317</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.728</v>
+        <v>-0.7223000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.728</v>
+        <v>-0.7223000000000001</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.728</v>
+        <v>-0.7223000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.728</v>
+        <v>-0.7223000000000001</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.728</v>
+        <v>-0.7223000000000001</v>
       </c>
       <c r="N59" t="n">
-        <v>99</v>
+        <v>79</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>yay</t>
+          <t>PERCY</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.7459</v>
+        <v>-0.728</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1947</v>
+        <v>-0.19</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7227</v>
+        <v>-0.7339</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.7459</v>
+        <v>-0.728</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.7459</v>
+        <v>-0.728</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.7459</v>
+        <v>-0.728</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.7459</v>
+        <v>-0.728</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.7459</v>
+        <v>-0.728</v>
       </c>
       <c r="N60" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>yay</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.7554</v>
+        <v>-0.7459</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1972</v>
+        <v>-0.1947</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7265</v>
+        <v>-0.7411</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.7554</v>
+        <v>-0.7459</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.7554</v>
+        <v>-0.7459</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.7554</v>
+        <v>-0.7459</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7554</v>
+        <v>-0.7459</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.7554</v>
+        <v>-0.7459</v>
       </c>
       <c r="N61" t="n">
-        <v>137</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.8781</v>
+        <v>-0.7554</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2292</v>
+        <v>-0.1972</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7761</v>
+        <v>-0.7449</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.8781</v>
+        <v>-0.7554</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.1226</v>
+        <v>-0.7554</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.7554999999999999</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.1226</v>
+        <v>-0.7554</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.1226</v>
+        <v>-0.7554</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.7554999999999999</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="L62" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.8781</v>
+        <v>-0.7554</v>
       </c>
       <c r="N62" t="n">
-        <v>225</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>pounh</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.8981</v>
+        <v>-0.8315</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2344</v>
+        <v>-0.2171</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7842</v>
+        <v>-0.7752</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.8981</v>
+        <v>-0.8315</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.8981</v>
+        <v>-0.076</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.8981</v>
+        <v>-0.076</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.8981</v>
+        <v>-0.076</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.8981</v>
+        <v>-0.8314999999999999</v>
       </c>
       <c r="N63" t="n">
-        <v>132</v>
+        <v>225</v>
       </c>
     </row>
     <row r="64">
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.918</v>
+        <v>-0.8468</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2396</v>
+        <v>-0.2211</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7922</v>
+        <v>-0.7813</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.918</v>
+        <v>-0.8468</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0286</v>
+        <v>0.0998</v>
       </c>
       <c r="G64" t="n">
         <v>-0.9466</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0286</v>
+        <v>0.0998</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0286</v>
+        <v>0.0998</v>
       </c>
       <c r="J64" t="n">
         <v>-0.9466</v>
@@ -3381,7 +3381,7 @@
         <v>50</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.918</v>
+        <v>-0.8468</v>
       </c>
       <c r="N64" t="n">
         <v>161</v>
@@ -3390,231 +3390,231 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>crush</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.9799</v>
+        <v>-0.8514</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2558</v>
+        <v>-0.2223</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8172</v>
+        <v>-0.7831</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.9799</v>
+        <v>-0.8514</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.6653</v>
+        <v>0.6006</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.3146</v>
+        <v>-1.452</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.6653</v>
+        <v>0.6006</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.6653</v>
+        <v>0.6006</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.3146</v>
+        <v>-1.452</v>
       </c>
       <c r="K65" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L65" t="n">
-        <v>55</v>
+        <v>269</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.9799</v>
+        <v>-0.8513999999999999</v>
       </c>
       <c r="N65" t="n">
-        <v>166</v>
+        <v>406</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>crush</t>
+          <t>dragonfly</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.0941</v>
+        <v>-0.9799</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2856</v>
+        <v>-0.2558</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8633999999999999</v>
+        <v>-0.8343</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.0941</v>
+        <v>-0.9799</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3579</v>
+        <v>-0.6653</v>
       </c>
       <c r="G66" t="n">
-        <v>-1.452</v>
+        <v>-0.3146</v>
       </c>
       <c r="H66" t="n">
-        <v>0.3579</v>
+        <v>-0.6653</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3579</v>
+        <v>-0.6653</v>
       </c>
       <c r="J66" t="n">
-        <v>-1.452</v>
+        <v>-0.3146</v>
       </c>
       <c r="K66" t="n">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L66" t="n">
-        <v>269</v>
+        <v>55</v>
       </c>
       <c r="M66" t="n">
-        <v>-1.0941</v>
+        <v>-0.9799</v>
       </c>
       <c r="N66" t="n">
-        <v>406</v>
+        <v>166</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Viva</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.0978</v>
+        <v>-0.9986</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.2866</v>
+        <v>-0.2607</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8648</v>
+        <v>-0.8418</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.0978</v>
+        <v>-0.9986</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.0978</v>
+        <v>-0.166</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>-0.8326</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.0978</v>
+        <v>-0.166</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0978</v>
+        <v>-0.166</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>-0.8326</v>
       </c>
       <c r="K67" t="n">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="M67" t="n">
-        <v>-1.0978</v>
+        <v>-0.9986</v>
       </c>
       <c r="N67" t="n">
-        <v>87</v>
+        <v>232</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>Viva</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.2254</v>
+        <v>-1.0977</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.3199</v>
+        <v>-0.2866</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9164</v>
+        <v>-0.8812</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.2254</v>
+        <v>-1.0977</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.6461</v>
+        <v>-1.0977</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.5793</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.6461</v>
+        <v>-1.0977</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.6461</v>
+        <v>-1.0977</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.5793</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="L68" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.2254</v>
+        <v>-1.0977</v>
       </c>
       <c r="N68" t="n">
-        <v>194</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.2848</v>
+        <v>-1.2254</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3354</v>
+        <v>-0.3199</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9404</v>
+        <v>-0.9321</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.2848</v>
+        <v>-1.2254</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.4522</v>
+        <v>-0.6461</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.8326</v>
+        <v>-0.5793</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.4522</v>
+        <v>-0.6461</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4522</v>
+        <v>-0.6461</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.8326</v>
+        <v>-0.5793</v>
       </c>
       <c r="K69" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="L69" t="n">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.2848</v>
+        <v>-1.2254</v>
       </c>
       <c r="N69" t="n">
-        <v>232</v>
+        <v>194</v>
       </c>
     </row>
     <row r="70">
@@ -3630,7 +3630,7 @@
         <v>-0.3362</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9416</v>
+        <v>-0.957</v>
       </c>
       <c r="E70" t="n">
         <v>-1.2878</v>
@@ -3676,7 +3676,7 @@
         <v>-0.3501</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9631</v>
+        <v>-0.9782</v>
       </c>
       <c r="E71" t="n">
         <v>-1.3411</v>
@@ -3712,47 +3712,47 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>HZ</t>
+          <t>torben</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.505</v>
+        <v>-1.3479</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.3929</v>
+        <v>-0.3519</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0293</v>
+        <v>-0.9809</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.505</v>
+        <v>-1.3479</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.505</v>
+        <v>-0.3479</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.505</v>
+        <v>-0.3479</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.505</v>
+        <v>-0.3479</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K72" t="n">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.505</v>
+        <v>-1.3479</v>
       </c>
       <c r="N72" t="n">
-        <v>87</v>
+        <v>166</v>
       </c>
     </row>
     <row r="73">
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.5334</v>
+        <v>-1.3866</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.4003</v>
+        <v>-0.362</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0408</v>
+        <v>-0.9963</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.5334</v>
+        <v>-1.3866</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.5334</v>
+        <v>-1.3866</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.5334</v>
+        <v>-1.3866</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.5334</v>
+        <v>-1.3866</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.5334</v>
+        <v>-1.3866</v>
       </c>
       <c r="N73" t="n">
         <v>141</v>
@@ -3804,47 +3804,47 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>torben</t>
+          <t>HZ</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.6069</v>
+        <v>-1.505</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.4195</v>
+        <v>-0.3929</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0705</v>
+        <v>-1.0435</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.6069</v>
+        <v>-1.505</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.6069</v>
+        <v>-1.505</v>
       </c>
       <c r="G74" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.6069</v>
+        <v>-1.505</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.6069</v>
+        <v>-1.505</v>
       </c>
       <c r="J74" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="L74" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.6069</v>
+        <v>-1.505</v>
       </c>
       <c r="N74" t="n">
-        <v>166</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75">
@@ -3860,7 +3860,7 @@
         <v>-0.4357</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0956</v>
+        <v>-1.1088</v>
       </c>
       <c r="E75" t="n">
         <v>-1.6689</v>
@@ -3906,7 +3906,7 @@
         <v>-0.4425</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1061</v>
+        <v>-1.1192</v>
       </c>
       <c r="E76" t="n">
         <v>-1.6949</v>
@@ -3952,7 +3952,7 @@
         <v>-0.5091</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2092</v>
+        <v>-1.2209</v>
       </c>
       <c r="E77" t="n">
         <v>-1.9503</v>
@@ -3998,7 +3998,7 @@
         <v>-0.5353</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2497</v>
+        <v>-1.2608</v>
       </c>
       <c r="E78" t="n">
         <v>-2.0504</v>
@@ -4044,7 +4044,7 @@
         <v>-0.5933</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3395</v>
+        <v>-1.3494</v>
       </c>
       <c r="E79" t="n">
         <v>-2.2727</v>
@@ -4090,7 +4090,7 @@
         <v>-0.5999</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3497</v>
+        <v>-1.3595</v>
       </c>
       <c r="E80" t="n">
         <v>-2.2981</v>
@@ -4136,7 +4136,7 @@
         <v>-0.7352</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5591</v>
+        <v>-1.5659</v>
       </c>
       <c r="E81" t="n">
         <v>-2.8163</v>
